--- a/CranioVentricleSeg/Statistics&images/paired_statistics_T1vsT2.xlsx
+++ b/CranioVentricleSeg/Statistics&images/paired_statistics_T1vsT2.xlsx
@@ -1,34 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manon\iCloudDrive\Bestanden\TM Master\TM stage\TM3 EMC ventricles\TM2_ventrikels_inference-1\CranioVentricleSeg\Statistics&amp;images\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6758CC-6335-48A8-A021-6C7DE4E19EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Ventricle</t>
+  </si>
+  <si>
+    <t>Median T1</t>
+  </si>
+  <si>
+    <t>T1 CI low</t>
+  </si>
+  <si>
+    <t>T1 CI high</t>
+  </si>
+  <si>
+    <t>Median T2</t>
+  </si>
+  <si>
+    <t>T2 CI low</t>
+  </si>
+  <si>
+    <t>T2 CI high</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>RV</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>3V</t>
+  </si>
+  <si>
+    <t>4V</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +98,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,154 +400,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RV_dice</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.96 (0.76-0.99)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.94 (0.62-0.98)</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.192092895507812e-07</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3V_dice</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.94 (0.85-0.97)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.84 (0.41-0.92)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5.960464477539062e-08</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4V_dice</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.93 (0.78-0.95)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.82 (0.31-0.90)</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1.192092895507812e-07</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CSP_dice</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.76 (0.38-0.87)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.47 (0.46-0.57)</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>0.95261317925</v>
+      </c>
+      <c r="C2">
+        <v>0.94634812300000004</v>
+      </c>
+      <c r="D2">
+        <v>0.97676322343749999</v>
+      </c>
+      <c r="E2">
+        <v>0.92185275919058407</v>
+      </c>
+      <c r="F2">
+        <v>0.878452494411466</v>
+      </c>
+      <c r="G2">
+        <v>0.96357608948815043</v>
+      </c>
+      <c r="H2">
+        <v>1.220703125E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>0.95944366099999989</v>
+      </c>
+      <c r="C3">
+        <v>0.95443154349999992</v>
+      </c>
+      <c r="D3">
+        <v>0.97773807599999996</v>
+      </c>
+      <c r="E3">
+        <v>0.93368017553890192</v>
+      </c>
+      <c r="F3">
+        <v>0.8885666936375024</v>
+      </c>
+      <c r="G3">
+        <v>0.95584238691849255</v>
+      </c>
+      <c r="H3">
+        <v>1.220703125E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0.93649965150000003</v>
+      </c>
+      <c r="C4">
+        <v>0.92475495000000008</v>
+      </c>
+      <c r="D4">
+        <v>0.94928516424999998</v>
+      </c>
+      <c r="E4">
+        <v>0.83616290772369362</v>
+      </c>
+      <c r="F4">
+        <v>0.77167726816203552</v>
+      </c>
+      <c r="G4">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="H4">
+        <v>1.220703125E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>0.92423439424999998</v>
+      </c>
+      <c r="C5">
+        <v>0.89668064575000006</v>
+      </c>
+      <c r="D5">
+        <v>0.93447588100000001</v>
+      </c>
+      <c r="E5">
+        <v>0.82646452208955634</v>
+      </c>
+      <c r="F5">
+        <v>0.73550078657577345</v>
+      </c>
+      <c r="G5">
+        <v>0.85878439673420015</v>
+      </c>
+      <c r="H5">
+        <v>2.44140625E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>0.68520331525</v>
+      </c>
+      <c r="C6">
+        <v>0.61521080849999998</v>
+      </c>
+      <c r="D6">
+        <v>0.75519582200000002</v>
+      </c>
+      <c r="E6">
+        <v>0.51956222686447495</v>
+      </c>
+      <c r="F6">
+        <v>0.46808651365831078</v>
+      </c>
+      <c r="G6">
+        <v>0.57103794007063913</v>
+      </c>
+      <c r="H6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LV_dice</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.96 (0.92-0.99)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.94 (0.77-0.98)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1.192092895507812e-07</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL_dice</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.96 (0.88-0.99)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.93 (0.72-0.98)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>5.960464477539062e-08</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>0.95302335199999999</v>
+      </c>
+      <c r="C7">
+        <v>0.94569700000000001</v>
+      </c>
+      <c r="D7">
+        <v>0.97255897925000001</v>
+      </c>
+      <c r="E7">
+        <v>0.91491657515180203</v>
+      </c>
+      <c r="F7">
+        <v>0.8894148914081641</v>
+      </c>
+      <c r="G7">
+        <v>0.9481983436801602</v>
+      </c>
+      <c r="H7">
+        <v>1.220703125E-4</v>
       </c>
     </row>
   </sheetData>
